--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/ARIZONA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/ARIZONA_2019.xlsx
@@ -2119,7 +2119,7 @@
         <v>11</v>
       </c>
       <c r="D98">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="99">
@@ -2263,7 +2263,7 @@
         <v>110</v>
       </c>
       <c r="D106">
-        <v>0.009473774868659031</v>
+        <v>0.009473774868659033</v>
       </c>
     </row>
     <row r="107">
@@ -2605,7 +2605,7 @@
         <v>11</v>
       </c>
       <c r="D125">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="126">
@@ -3307,7 +3307,7 @@
         <v>11</v>
       </c>
       <c r="D164">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="165">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C287">
@@ -5791,7 +5791,7 @@
         <v>11</v>
       </c>
       <c r="D302">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="303">
@@ -5827,7 +5827,7 @@
         <v>11</v>
       </c>
       <c r="D304">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="305">
@@ -6439,7 +6439,7 @@
         <v>11</v>
       </c>
       <c r="D338">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="339">
@@ -6691,7 +6691,7 @@
         <v>11</v>
       </c>
       <c r="D352">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="353">
@@ -6727,7 +6727,7 @@
         <v>11</v>
       </c>
       <c r="D354">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="355">
@@ -7033,7 +7033,7 @@
         <v>11</v>
       </c>
       <c r="D371">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="372">
@@ -9355,7 +9355,7 @@
         <v>11</v>
       </c>
       <c r="D500">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="501">
@@ -10291,7 +10291,7 @@
         <v>11</v>
       </c>
       <c r="D552">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="553">
@@ -10993,7 +10993,7 @@
         <v>11</v>
       </c>
       <c r="D591">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="592">
@@ -11497,7 +11497,7 @@
         <v>11</v>
       </c>
       <c r="D619">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="620">
@@ -11803,7 +11803,7 @@
         <v>11</v>
       </c>
       <c r="D636">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="637">
@@ -12019,7 +12019,7 @@
         <v>11</v>
       </c>
       <c r="D648">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="649">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C728">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C749">
@@ -15907,7 +15907,7 @@
         <v>11</v>
       </c>
       <c r="D864">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="865">
@@ -18229,7 +18229,7 @@
         <v>11</v>
       </c>
       <c r="D993">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="994">
@@ -18535,7 +18535,7 @@
         <v>11</v>
       </c>
       <c r="D1010">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="1011">
@@ -21037,7 +21037,7 @@
         <v>11</v>
       </c>
       <c r="D1149">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="1150">
@@ -21811,7 +21811,7 @@
         <v>11</v>
       </c>
       <c r="D1192">
-        <v>0.0009473774868659031</v>
+        <v>0.0009473774868659032</v>
       </c>
     </row>
     <row r="1193">
